--- a/docs/ISE 5763 Capstone Project.xlsx
+++ b/docs/ISE 5763 Capstone Project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emmanuelakinwale/Developer/pm-substrate/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9282F34E-1435-2A4B-B854-CE9DE1E4F8F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F1E510-F060-1346-9DAE-64131B9763B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="2" xr2:uid="{F66B4C7C-1CA9-2141-B218-190A95B577B9}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="3" xr2:uid="{F66B4C7C-1CA9-2141-B218-190A95B577B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="Project Definition" sheetId="3" r:id="rId3"/>
     <sheet name="Token Savings Model" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -449,7 +450,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="225">
   <si>
     <t>Capstone project must involve a comprehensive analysis of a project management topic</t>
   </si>
@@ -1084,9 +1085,6 @@
     <t>In Progress</t>
   </si>
   <si>
-    <t>Idea formulated &amp; scored 18/20 on Project Definition sheet; Step 2 selection drafted. Next: submit for Week-4 approval.</t>
-  </si>
-  <si>
     <t>Complete</t>
   </si>
   <si>
@@ -1145,6 +1143,12 @@
   </si>
   <si>
     <t>Real, individually-run open-source software project: the pm-substrate GitHub repo (typed events, graph-based state, read-set validation, observation contracts, eval scenarios, Local Agents Lab Enviroment as TestBed then a Financial Hedge Fund for research and trading - which requests high in/out flow of data constantly,  finance-adapter example). Peer input welcomed on scope, PM metrics, and non-technical presentation.</t>
+  </si>
+  <si>
+    <t>Selection submitted 7/19/2026 — awaiting instructor approval. Mark Complete and fill Topic Approved date (D8) when instructor signs off.</t>
+  </si>
+  <si>
+    <t>Idea formulated &amp; scored 18/20 on Project Definition sheet; selection submitted 7/19/2026.</t>
   </si>
 </sst>
 </file>
@@ -1152,9 +1156,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -1366,16 +1370,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1384,9 +1384,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
@@ -1421,12 +1418,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1439,22 +1430,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1466,9 +1442,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1477,20 +1450,50 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1551,10 +1554,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1904,39 +1903,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
@@ -1955,7 +1954,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="7" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1976,7 +1975,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="7" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2005,17 +2004,17 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B18" s="7">
+      <c r="B18" s="5">
         <v>1</v>
       </c>
       <c r="C18" t="s">
@@ -2023,7 +2022,7 @@
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B19" s="7">
+      <c r="B19" s="5">
         <v>2</v>
       </c>
       <c r="C19" t="s">
@@ -2031,7 +2030,7 @@
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B20" s="7">
+      <c r="B20" s="5">
         <v>3</v>
       </c>
       <c r="C20" t="s">
@@ -2039,10 +2038,10 @@
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B21" s="6"/>
+      <c r="B21" s="4"/>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="4" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2127,10 +2126,10 @@
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B34" s="6"/>
+      <c r="B34" s="4"/>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="4" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2159,13 +2158,13 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B39" s="6"/>
+      <c r="B39" s="4"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B40" s="6"/>
+      <c r="B40" s="4"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="4" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2186,18 +2185,18 @@
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="8"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="54"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="54"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="54"/>
+      <c r="K45" s="54"/>
+      <c r="L45" s="54"/>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
@@ -2382,6 +2381,7 @@
     <mergeCell ref="C45:L45"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -2401,511 +2401,505 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="5"/>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="3"/>
+      <c r="B4" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="22" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="G4" s="12" t="str">
+      <c r="G4" s="9" t="str">
         <f>COUNTIF(G11:G29,"Complete")&amp;" / "&amp;COUNTA(G11:G29)&amp;" complete ("&amp;TEXT(COUNTIF(G11:G29,"Complete")/COUNTA(G11:G29),"0%")&amp;")"</f>
-        <v>1 / 19 complete (5%)</v>
+        <v>2 / 19 complete (11%)</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="5"/>
-      <c r="B5" s="21" t="s">
+      <c r="A5" s="3"/>
+      <c r="B5" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="22" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="19" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="5"/>
-      <c r="B6" s="21" t="s">
+      <c r="A6" s="3"/>
+      <c r="B6" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="22" t="s">
+      <c r="C6" s="3"/>
+      <c r="D6" s="19" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="5"/>
-      <c r="B7" s="21" t="s">
+      <c r="A7" s="3"/>
+      <c r="B7" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="22" t="s">
+      <c r="C7" s="3"/>
+      <c r="D7" s="19" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="5"/>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="3"/>
+      <c r="B8" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="22"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="19"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="13" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A11" s="17">
+      <c r="A11" s="14">
         <v>1</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="19"/>
-      <c r="F11" s="17">
+      <c r="E11" s="16"/>
+      <c r="F11" s="14">
         <v>4</v>
       </c>
-      <c r="G11" s="17" t="s">
+      <c r="G11" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="14">
+        <v>2</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" s="16"/>
+      <c r="F12" s="14">
+        <v>4</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A13" s="14">
+        <v>3</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="16"/>
+      <c r="F13" s="14">
+        <v>4</v>
+      </c>
+      <c r="G13" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="H11" s="19" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="17">
-        <v>2</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="E12" s="19"/>
-      <c r="F12" s="17">
+      <c r="H13" s="16" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="14">
         <v>4</v>
       </c>
-      <c r="G12" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="17">
-        <v>3</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" s="19"/>
-      <c r="F13" s="17">
-        <v>4</v>
-      </c>
-      <c r="G13" s="17" t="s">
+      <c r="B14" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="16"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="H13" s="19"/>
-    </row>
-    <row r="14" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="17">
-        <v>4</v>
-      </c>
-      <c r="B14" s="18" t="s">
+      <c r="H14" s="16"/>
+    </row>
+    <row r="15" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="14">
+        <v>5</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="16"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H15" s="16"/>
+    </row>
+    <row r="16" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" s="14">
+        <v>6</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" s="16"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="16"/>
+    </row>
+    <row r="17" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" s="14">
+        <v>7</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="16"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H17" s="16"/>
+    </row>
+    <row r="18" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" s="14">
+        <v>8</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" s="16"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H18" s="16"/>
+    </row>
+    <row r="19" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A19" s="14">
+        <v>9</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="16"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H19" s="16"/>
+    </row>
+    <row r="20" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A20" s="14">
+        <v>10</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" s="16"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H20" s="16"/>
+    </row>
+    <row r="21" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A21" s="14">
+        <v>11</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="E21" s="16"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H21" s="16"/>
+    </row>
+    <row r="22" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A22" s="14">
+        <v>12</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" s="16"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H22" s="16"/>
+    </row>
+    <row r="23" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A23" s="14">
+        <v>13</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23" s="16"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H23" s="16"/>
+    </row>
+    <row r="24" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A24" s="14">
+        <v>14</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E24" s="16"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="16"/>
+    </row>
+    <row r="25" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A25" s="14">
+        <v>15</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E25" s="16"/>
+      <c r="F25" s="14">
+        <v>13</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H25" s="16"/>
+    </row>
+    <row r="26" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A26" s="14">
+        <v>16</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="E26" s="16"/>
+      <c r="F26" s="14">
+        <v>13</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H26" s="16"/>
+    </row>
+    <row r="27" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A27" s="14">
         <v>17</v>
       </c>
-      <c r="C14" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="E14" s="19"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17" t="s">
+      <c r="B27" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" s="16"/>
+      <c r="F27" s="14">
+        <v>14</v>
+      </c>
+      <c r="G27" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="H14" s="19"/>
-    </row>
-    <row r="15" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="17">
-        <v>5</v>
-      </c>
-      <c r="B15" s="18" t="s">
+      <c r="H27" s="16"/>
+    </row>
+    <row r="28" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A28" s="14">
         <v>18</v>
       </c>
-      <c r="C15" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" s="19"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17" t="s">
+      <c r="B28" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="E28" s="16"/>
+      <c r="F28" s="14">
+        <v>14</v>
+      </c>
+      <c r="G28" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="H15" s="19"/>
-    </row>
-    <row r="16" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="17">
-        <v>6</v>
-      </c>
-      <c r="B16" s="18" t="s">
+      <c r="H28" s="16"/>
+    </row>
+    <row r="29" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A29" s="14">
         <v>19</v>
       </c>
-      <c r="C16" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" s="19"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17" t="s">
+      <c r="B29" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E29" s="16"/>
+      <c r="F29" s="14">
+        <v>14</v>
+      </c>
+      <c r="G29" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="H16" s="19"/>
-    </row>
-    <row r="17" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="17">
-        <v>7</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="E17" s="19"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H17" s="19"/>
-    </row>
-    <row r="18" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A18" s="17">
-        <v>8</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="E18" s="19"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H18" s="19"/>
-    </row>
-    <row r="19" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A19" s="17">
-        <v>9</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="E19" s="19"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H19" s="19"/>
-    </row>
-    <row r="20" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A20" s="17">
-        <v>10</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" s="19"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H20" s="19"/>
-    </row>
-    <row r="21" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A21" s="17">
-        <v>11</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E21" s="19"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H21" s="19"/>
-    </row>
-    <row r="22" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A22" s="17">
-        <v>12</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="E22" s="19"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H22" s="19"/>
-    </row>
-    <row r="23" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A23" s="17">
-        <v>13</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="E23" s="19"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H23" s="19"/>
-    </row>
-    <row r="24" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A24" s="17">
-        <v>14</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="E24" s="19"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H24" s="19"/>
-    </row>
-    <row r="25" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="17">
-        <v>15</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="E25" s="19"/>
-      <c r="F25" s="17">
-        <v>13</v>
-      </c>
-      <c r="G25" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H25" s="19"/>
-    </row>
-    <row r="26" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A26" s="17">
-        <v>16</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="E26" s="19"/>
-      <c r="F26" s="17">
-        <v>13</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H26" s="19"/>
-    </row>
-    <row r="27" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A27" s="17">
-        <v>17</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="E27" s="19"/>
-      <c r="F27" s="17">
-        <v>14</v>
-      </c>
-      <c r="G27" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H27" s="19"/>
-    </row>
-    <row r="28" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A28" s="17">
-        <v>18</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="E28" s="19"/>
-      <c r="F28" s="17">
-        <v>14</v>
-      </c>
-      <c r="G28" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H28" s="19"/>
-    </row>
-    <row r="29" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A29" s="17">
-        <v>19</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="E29" s="19"/>
-      <c r="F29" s="17">
-        <v>14</v>
-      </c>
-      <c r="G29" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H29" s="19"/>
+      <c r="H29" s="16"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G11:G29">
     <cfRule type="expression" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11:G29">
     <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",G11)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11:G29">
     <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="In Progress">
       <formula>NOT(ISERROR(SEARCH("In Progress",G11)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11:G29">
     <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Blocked">
       <formula>NOT(ISERROR(SEARCH("Blocked",G11)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11:G29">
     <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Not Started">
       <formula>NOT(ISERROR(SEARCH("Not Started",G11)))</formula>
     </cfRule>
@@ -2916,6 +2910,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -2932,576 +2927,578 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="22" x14ac:dyDescent="0.2">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="22" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="30" t="s">
         <v>171</v>
       </c>
-      <c r="C6" s="40">
+      <c r="C6" s="29">
         <v>4</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="29">
         <v>5</v>
       </c>
-      <c r="E6" s="40">
+      <c r="E6" s="29">
         <v>5</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="29">
         <v>4</v>
       </c>
-      <c r="G6" s="29">
+      <c r="G6" s="24">
         <f>IF(COUNT(C6:F6)=0,"",SUM(C6:F6))</f>
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="28"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="29" t="str">
+      <c r="B7" s="23"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="24" t="str">
         <f t="shared" ref="G7:G8" si="0">IF(COUNT(C7:F7)=0,"",SUM(C7:F7))</f>
         <v/>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="28"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="29" t="str">
+      <c r="B8" s="23"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="24" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="51" t="s">
         <v>134</v>
       </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="49" t="s">
         <v>135</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
     </row>
     <row r="12" spans="2:7" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="46" t="s">
         <v>172</v>
       </c>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
     </row>
     <row r="13" spans="2:7" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="46" t="s">
         <v>173</v>
       </c>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
     </row>
     <row r="14" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="C14" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
+      <c r="C14" s="46" t="s">
+        <v>222</v>
+      </c>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
     </row>
     <row r="15" spans="2:7" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
     </row>
     <row r="16" spans="2:7" ht="67" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="46" t="s">
         <v>175</v>
       </c>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="52" t="s">
         <v>141</v>
       </c>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="52"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="49" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="49"/>
     </row>
     <row r="20" spans="2:7" ht="69" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="46" t="s">
         <v>176</v>
       </c>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="20"/>
-      <c r="C21" s="34" t="s">
+      <c r="B21" s="17"/>
+      <c r="C21" s="47" t="s">
         <v>144</v>
       </c>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34" t="s">
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47" t="s">
         <v>145</v>
       </c>
-      <c r="G21" s="34"/>
+      <c r="G21" s="47"/>
     </row>
     <row r="22" spans="2:7" ht="79" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="33" t="s">
+      <c r="B22" s="25" t="s">
         <v>146</v>
       </c>
-      <c r="C22" s="35" t="str">
+      <c r="C22" s="48" t="str">
         <f>Sheet1!C12</f>
         <v>Describe the planning and execution of a complex project incorporating a management approach. (MLO 1, 2; CLO A, E)</v>
       </c>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="31" t="s">
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="46" t="s">
         <v>177</v>
       </c>
-      <c r="G22" s="31"/>
+      <c r="G22" s="46"/>
     </row>
     <row r="23" spans="2:7" ht="70" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="25" t="s">
         <v>147</v>
       </c>
-      <c r="C23" s="35" t="str">
+      <c r="C23" s="48" t="str">
         <f>Sheet1!C13</f>
         <v>Develop a comprehensive project plan that includes budgeting, scheduling, and resource allocation. (MLO 2, 2;CLO D, E)</v>
       </c>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="31" t="s">
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="46" t="s">
         <v>178</v>
       </c>
-      <c r="G23" s="31"/>
+      <c r="G23" s="46"/>
     </row>
     <row r="24" spans="2:7" ht="53" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="33" t="s">
+      <c r="B24" s="25" t="s">
         <v>148</v>
       </c>
-      <c r="C24" s="35" t="str">
+      <c r="C24" s="48" t="str">
         <f>Sheet1!C14</f>
         <v>Analyze a complex project and develop documentation of the process  for transitioning the project to operational status. (MLO1, 2; CLO D, E)</v>
       </c>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="31" t="s">
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="G24" s="31"/>
+      <c r="G24" s="46"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B26" s="25" t="s">
+      <c r="B26" s="49" t="s">
         <v>149</v>
       </c>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B27" s="26" t="s">
+      <c r="B27" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="C27" s="34" t="s">
+      <c r="C27" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34" t="s">
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47" t="s">
         <v>152</v>
       </c>
-      <c r="G27" s="34"/>
+      <c r="G27" s="47"/>
     </row>
     <row r="28" spans="2:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="33" t="s">
+      <c r="B28" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="31" t="s">
+      <c r="C28" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31" t="s">
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="G28" s="31"/>
+      <c r="G28" s="46"/>
     </row>
     <row r="29" spans="2:7" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="33" t="s">
+      <c r="B29" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="31" t="s">
+      <c r="C29" s="46" t="s">
         <v>182</v>
       </c>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31" t="s">
+      <c r="D29" s="46"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46" t="s">
         <v>183</v>
       </c>
-      <c r="G29" s="31"/>
+      <c r="G29" s="46"/>
     </row>
     <row r="30" spans="2:7" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="33" t="s">
+      <c r="B30" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="31" t="s">
+      <c r="C30" s="46" t="s">
+        <v>205</v>
+      </c>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46" t="s">
+        <v>184</v>
+      </c>
+      <c r="G30" s="46"/>
+    </row>
+    <row r="31" spans="2:7" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="46" t="s">
+        <v>185</v>
+      </c>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46" t="s">
+        <v>186</v>
+      </c>
+      <c r="G31" s="46"/>
+    </row>
+    <row r="32" spans="2:7" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="46" t="s">
+        <v>187</v>
+      </c>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46" t="s">
+        <v>188</v>
+      </c>
+      <c r="G32" s="46"/>
+    </row>
+    <row r="33" spans="2:7" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" s="46" t="s">
         <v>206</v>
       </c>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="G30" s="31"/>
-    </row>
-    <row r="31" spans="2:7" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31" s="31" t="s">
-        <v>185</v>
-      </c>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="G31" s="31"/>
-    </row>
-    <row r="32" spans="2:7" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="C32" s="31" t="s">
-        <v>187</v>
-      </c>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="G32" s="31"/>
-    </row>
-    <row r="33" spans="2:7" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="C33" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31" t="s">
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46" t="s">
         <v>189</v>
       </c>
-      <c r="G33" s="31"/>
+      <c r="G33" s="46"/>
     </row>
     <row r="34" spans="2:7" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="33" t="s">
+      <c r="B34" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="C34" s="31" t="s">
+      <c r="C34" s="46" t="s">
         <v>190</v>
       </c>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31" t="s">
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46" t="s">
         <v>191</v>
       </c>
-      <c r="G34" s="31"/>
+      <c r="G34" s="46"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B36" s="25" t="s">
+      <c r="B36" s="49" t="s">
         <v>155</v>
       </c>
-      <c r="C36" s="25"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
+      <c r="C36" s="49"/>
+      <c r="D36" s="49"/>
+      <c r="E36" s="49"/>
+      <c r="F36" s="49"/>
+      <c r="G36" s="49"/>
     </row>
     <row r="37" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B37" s="36" t="s">
+      <c r="B37" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="C37" s="37" t="s">
+      <c r="C37" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="D37" s="34" t="s">
+      <c r="D37" s="47" t="s">
         <v>157</v>
       </c>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34" t="s">
+      <c r="E37" s="47"/>
+      <c r="F37" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="G37" s="34"/>
+      <c r="G37" s="47"/>
     </row>
     <row r="38" spans="2:7" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="20" t="s">
+      <c r="B38" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="C38" s="38">
+      <c r="C38" s="28">
         <v>20</v>
       </c>
-      <c r="D38" s="39" t="s">
+      <c r="D38" s="45" t="s">
         <v>160</v>
       </c>
-      <c r="E38" s="39"/>
-      <c r="F38" s="31" t="s">
+      <c r="E38" s="45"/>
+      <c r="F38" s="46" t="s">
         <v>192</v>
       </c>
-      <c r="G38" s="31"/>
+      <c r="G38" s="46"/>
     </row>
     <row r="39" spans="2:7" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="20" t="s">
+      <c r="B39" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="C39" s="38">
+      <c r="C39" s="28">
         <v>30</v>
       </c>
-      <c r="D39" s="39" t="s">
+      <c r="D39" s="45" t="s">
         <v>162</v>
       </c>
-      <c r="E39" s="39"/>
-      <c r="F39" s="31" t="s">
+      <c r="E39" s="45"/>
+      <c r="F39" s="46" t="s">
         <v>193</v>
       </c>
-      <c r="G39" s="31"/>
+      <c r="G39" s="46"/>
     </row>
     <row r="40" spans="2:7" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="20" t="s">
+      <c r="B40" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="C40" s="38">
+      <c r="C40" s="28">
         <v>20</v>
       </c>
-      <c r="D40" s="39" t="s">
+      <c r="D40" s="45" t="s">
         <v>164</v>
       </c>
-      <c r="E40" s="39"/>
-      <c r="F40" s="31" t="s">
+      <c r="E40" s="45"/>
+      <c r="F40" s="46" t="s">
         <v>194</v>
       </c>
-      <c r="G40" s="31"/>
+      <c r="G40" s="46"/>
     </row>
     <row r="41" spans="2:7" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="C41" s="38">
+      <c r="C41" s="28">
         <v>15</v>
       </c>
-      <c r="D41" s="39" t="s">
+      <c r="D41" s="45" t="s">
         <v>166</v>
       </c>
-      <c r="E41" s="39"/>
-      <c r="F41" s="31" t="s">
+      <c r="E41" s="45"/>
+      <c r="F41" s="46" t="s">
         <v>195</v>
       </c>
-      <c r="G41" s="31"/>
+      <c r="G41" s="46"/>
     </row>
     <row r="42" spans="2:7" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="20" t="s">
+      <c r="B42" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="C42" s="38">
+      <c r="C42" s="28">
         <v>10</v>
       </c>
-      <c r="D42" s="39" t="s">
+      <c r="D42" s="45" t="s">
         <v>168</v>
       </c>
-      <c r="E42" s="39"/>
-      <c r="F42" s="31" t="s">
+      <c r="E42" s="45"/>
+      <c r="F42" s="46" t="s">
         <v>196</v>
       </c>
-      <c r="G42" s="31"/>
+      <c r="G42" s="46"/>
     </row>
     <row r="43" spans="2:7" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="20" t="s">
+      <c r="B43" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="C43" s="38">
+      <c r="C43" s="28">
         <v>5</v>
       </c>
-      <c r="D43" s="39" t="s">
+      <c r="D43" s="45" t="s">
         <v>170</v>
       </c>
-      <c r="E43" s="39"/>
-      <c r="F43" s="31" t="s">
+      <c r="E43" s="45"/>
+      <c r="F43" s="46" t="s">
         <v>197</v>
       </c>
-      <c r="G43" s="31"/>
+      <c r="G43" s="46"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B44" s="18" t="s">
+      <c r="B44" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C44" s="24">
         <f>SUM(C38:C43)</f>
         <v>100</v>
       </c>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="F24:G24"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="D37:E37"/>
@@ -3512,28 +3509,26 @@
     <mergeCell ref="F29:G29"/>
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="F30:G30"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="F42:G42"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C13" xr:uid="{9326FE6E-EF18-4041-A157-CE005506834D}">
@@ -3545,6 +3540,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3560,278 +3556,279 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="22" x14ac:dyDescent="0.3">
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B3" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B3" s="42" t="s">
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B5" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B5" s="23" t="s">
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B6" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B6" s="13" t="s">
+      <c r="C6" s="32">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B7" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="C6" s="43">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="13" t="s">
+      <c r="C7" s="33">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B8" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="C7" s="44">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="13" t="s">
+      <c r="C8" s="33">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B9" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="C8" s="44">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B9" s="13" t="s">
+      <c r="C9" s="32">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B10" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="C9" s="43">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B10" s="13" t="s">
+      <c r="C10" s="34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B12" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="C10" s="45">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="23" t="s">
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B13" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="C13" s="46">
+      <c r="C13" s="35">
         <f>C6*(C7-C8)</f>
         <v>169.99999999999997</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="C14" s="46">
+      <c r="B14" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="C14" s="35">
         <f>C13*C9</f>
         <v>2549999.9999999995</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="C15" s="47">
+      <c r="B15" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="C15" s="36">
         <f>C14/1000000*C10</f>
         <v>7.6499999999999986</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B16" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="C16" s="48">
+      <c r="B16" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C16" s="37">
         <f>C15*12</f>
         <v>91.799999999999983</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B19" s="38" t="s">
         <v>221</v>
       </c>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="49" t="s">
-        <v>222</v>
-      </c>
-      <c r="C19" s="50">
+      <c r="C19" s="39">
         <v>1</v>
       </c>
-      <c r="D19" s="50">
+      <c r="D19" s="39">
         <v>2</v>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="39">
         <v>3</v>
       </c>
-      <c r="F19" s="50">
+      <c r="F19" s="39">
         <v>4</v>
       </c>
-      <c r="G19" s="50">
+      <c r="G19" s="39">
         <v>5</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B20" s="51">
+      <c r="B20" s="40">
         <v>250</v>
       </c>
-      <c r="C20" s="47">
+      <c r="C20" s="36">
         <f>$B20*($C$7-$C$8)*$C$9/1000000*C$19*12</f>
         <v>7.6499999999999986</v>
       </c>
-      <c r="D20" s="47">
+      <c r="D20" s="36">
         <f t="shared" ref="D20:G24" si="0">$B20*($C$7-$C$8)*$C$9/1000000*D$19*12</f>
         <v>15.299999999999997</v>
       </c>
-      <c r="E20" s="47">
+      <c r="E20" s="36">
         <f t="shared" si="0"/>
         <v>22.949999999999996</v>
       </c>
-      <c r="F20" s="47">
+      <c r="F20" s="36">
         <f t="shared" si="0"/>
         <v>30.599999999999994</v>
       </c>
-      <c r="G20" s="47">
+      <c r="G20" s="36">
         <f t="shared" si="0"/>
         <v>38.249999999999986</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="51">
+      <c r="B21" s="40">
         <v>500</v>
       </c>
-      <c r="C21" s="47">
-        <f t="shared" ref="C21:G24" si="1">$B21*($C$7-$C$8)*$C$9/1000000*C$19*12</f>
+      <c r="C21" s="36">
+        <f t="shared" ref="C21:C24" si="1">$B21*($C$7-$C$8)*$C$9/1000000*C$19*12</f>
         <v>15.299999999999997</v>
       </c>
-      <c r="D21" s="47">
+      <c r="D21" s="36">
         <f t="shared" si="0"/>
         <v>30.599999999999994</v>
       </c>
-      <c r="E21" s="47">
+      <c r="E21" s="36">
         <f t="shared" si="0"/>
         <v>45.899999999999991</v>
       </c>
-      <c r="F21" s="47">
+      <c r="F21" s="36">
         <f t="shared" si="0"/>
         <v>61.199999999999989</v>
       </c>
-      <c r="G21" s="47">
+      <c r="G21" s="36">
         <f t="shared" si="0"/>
         <v>76.499999999999972</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B22" s="51">
+      <c r="B22" s="40">
         <v>1000</v>
       </c>
-      <c r="C22" s="47">
+      <c r="C22" s="36">
         <f t="shared" si="1"/>
         <v>30.599999999999994</v>
       </c>
-      <c r="D22" s="47">
+      <c r="D22" s="36">
         <f t="shared" si="0"/>
         <v>61.199999999999989</v>
       </c>
-      <c r="E22" s="52">
+      <c r="E22" s="41">
         <f t="shared" si="0"/>
         <v>91.799999999999983</v>
       </c>
-      <c r="F22" s="47">
+      <c r="F22" s="36">
         <f t="shared" si="0"/>
         <v>122.39999999999998</v>
       </c>
-      <c r="G22" s="47">
+      <c r="G22" s="36">
         <f t="shared" si="0"/>
         <v>152.99999999999994</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B23" s="51">
+      <c r="B23" s="40">
         <v>2000</v>
       </c>
-      <c r="C23" s="47">
+      <c r="C23" s="36">
         <f t="shared" si="1"/>
         <v>61.199999999999989</v>
       </c>
-      <c r="D23" s="47">
+      <c r="D23" s="36">
         <f t="shared" si="0"/>
         <v>122.39999999999998</v>
       </c>
-      <c r="E23" s="47">
+      <c r="E23" s="36">
         <f t="shared" si="0"/>
         <v>183.59999999999997</v>
       </c>
-      <c r="F23" s="47">
+      <c r="F23" s="36">
         <f t="shared" si="0"/>
         <v>244.79999999999995</v>
       </c>
-      <c r="G23" s="47">
+      <c r="G23" s="36">
         <f t="shared" si="0"/>
         <v>305.99999999999989</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B24" s="51">
+      <c r="B24" s="40">
         <v>4000</v>
       </c>
-      <c r="C24" s="47">
+      <c r="C24" s="36">
         <f t="shared" si="1"/>
         <v>122.39999999999998</v>
       </c>
-      <c r="D24" s="47">
+      <c r="D24" s="36">
         <f t="shared" si="0"/>
         <v>244.79999999999995</v>
       </c>
-      <c r="E24" s="47">
+      <c r="E24" s="36">
         <f t="shared" si="0"/>
         <v>367.19999999999993</v>
       </c>
-      <c r="F24" s="47">
+      <c r="F24" s="36">
         <f t="shared" si="0"/>
         <v>489.59999999999991</v>
       </c>
-      <c r="G24" s="47">
+      <c r="G24" s="36">
         <f t="shared" si="0"/>
         <v>611.99999999999977</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>